--- a/Revision Process.xlsx
+++ b/Revision Process.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18615" windowHeight="13065"/>
+    <workbookView windowWidth="27945" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>Release Version</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Pseudo OMM  흔들리는 현상</t>
+  </si>
+  <si>
+    <t>4Line 전용 프로그램 관리 및 현장 알고리즘 수정</t>
   </si>
 </sst>
 </file>
@@ -987,7 +990,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1507,7 +1510,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:D28"/>
+  <dimension ref="B2:D29"/>
   <sheetFormatPr defaultColWidth="9.12380952380952" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="16.6285714285714" style="1" customWidth="1"/>
@@ -1802,6 +1805,17 @@
         <v>47</v>
       </c>
     </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="1">
+        <v>26070701</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Revision Process.xlsx
+++ b/Revision Process.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
   <si>
     <t>Release Version</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>4Line 전용 프로그램 관리 및 현장 알고리즘 수정</t>
+  </si>
+  <si>
+    <t>Pseudo OMM 추가 요청 ( TZ )</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D30"/>
   <sheetFormatPr defaultColWidth="9.12380952380952" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="16.6285714285714" style="1" customWidth="1"/>
@@ -1807,12 +1810,23 @@
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="1">
-        <v>26070701</v>
+        <v>26070101</v>
       </c>
       <c r="C29" t="s">
         <v>49</v>
       </c>
       <c r="D29" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="1">
+        <v>26070701</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="16" t="s">
         <v>47</v>
       </c>
     </row>
